--- a/CSV2SHP/VLOC3 TEMA KODER.xlsx
+++ b/CSV2SHP/VLOC3 TEMA KODER.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29203"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="82" documentId="11_9C5455BF84DCCE936262E6F99831F45BBA780A8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF546106-BA1E-40CF-8828-A0FA9A3814EC}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="11_9C5455BF84DCCE936262E6F99831F45BBA780A8F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB99CD8B-7D86-42DC-BB16-42CAB5C4F5B3}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,6 +87,12 @@
     <t>798</t>
   </si>
   <si>
+    <t>324 - Trasepunkt landmålte punkt</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
     <t>360 - Trasepunkt mast LSP</t>
   </si>
   <si>
@@ -175,12 +181,6 @@
   </si>
   <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>324 - Trasepunkt landmålte punkt</t>
-  </si>
-  <si>
-    <t>324</t>
   </si>
   <si>
     <t>325 - Trase innm. situasjon</t>
